--- a/LME/parser/cbr/data/cb_metalls.xlsx
+++ b/LME/parser/cbr/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E913"/>
+  <dimension ref="A1:E914"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -15914,6 +15914,23 @@
         <v>3523.49</v>
       </c>
     </row>
+    <row r="914" spans="1:5">
+      <c r="A914" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B914">
+        <v>11893.2</v>
+      </c>
+      <c r="C914">
+        <v>173.1</v>
+      </c>
+      <c r="D914">
+        <v>4898.41</v>
+      </c>
+      <c r="E914">
+        <v>3581.18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_metalls.xlsx
+++ b/LME/parser/cbr/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E914"/>
+  <dimension ref="A1:E915"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -15931,6 +15931,23 @@
         <v>3581.18</v>
       </c>
     </row>
+    <row r="915" spans="1:5">
+      <c r="A915" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B915">
+        <v>11556.39</v>
+      </c>
+      <c r="C915">
+        <v>170.11</v>
+      </c>
+      <c r="D915">
+        <v>4777.36</v>
+      </c>
+      <c r="E915">
+        <v>3494.87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_metalls.xlsx
+++ b/LME/parser/cbr/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E915"/>
+  <dimension ref="A1:E916"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -15948,6 +15948,23 @@
         <v>3494.87</v>
       </c>
     </row>
+    <row r="916" spans="1:5">
+      <c r="A916" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B916">
+        <v>11626.37</v>
+      </c>
+      <c r="C916">
+        <v>170.95</v>
+      </c>
+      <c r="D916">
+        <v>4811.4</v>
+      </c>
+      <c r="E916">
+        <v>3528.92</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_metalls.xlsx
+++ b/LME/parser/cbr/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E916"/>
+  <dimension ref="A1:E917"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -15965,6 +15965,23 @@
         <v>3528.92</v>
       </c>
     </row>
+    <row r="917" spans="1:5">
+      <c r="A917" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B917">
+        <v>11759.87</v>
+      </c>
+      <c r="C917">
+        <v>175.91</v>
+      </c>
+      <c r="D917">
+        <v>4874.5</v>
+      </c>
+      <c r="E917">
+        <v>3544.37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_metalls.xlsx
+++ b/LME/parser/cbr/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E917"/>
+  <dimension ref="A1:E918"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -15982,6 +15982,23 @@
         <v>3544.37</v>
       </c>
     </row>
+    <row r="918" spans="1:5">
+      <c r="A918" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B918">
+        <v>11824.49</v>
+      </c>
+      <c r="C918">
+        <v>173.59</v>
+      </c>
+      <c r="D918">
+        <v>4862.87</v>
+      </c>
+      <c r="E918">
+        <v>3519.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_metalls.xlsx
+++ b/LME/parser/cbr/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E918"/>
+  <dimension ref="A1:E919"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -15999,6 +15999,23 @@
         <v>3519.79</v>
       </c>
     </row>
+    <row r="919" spans="1:5">
+      <c r="A919" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B919">
+        <v>11756.21</v>
+      </c>
+      <c r="C919">
+        <v>181.24</v>
+      </c>
+      <c r="D919">
+        <v>4848.32</v>
+      </c>
+      <c r="E919">
+        <v>3556.75</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_metalls.xlsx
+++ b/LME/parser/cbr/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E919"/>
+  <dimension ref="A1:E920"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -16016,6 +16016,23 @@
         <v>3556.75</v>
       </c>
     </row>
+    <row r="920" spans="1:5">
+      <c r="A920" s="2">
+        <v>46288</v>
+      </c>
+      <c r="B920">
+        <v>11687.47</v>
+      </c>
+      <c r="C920">
+        <v>178.05</v>
+      </c>
+      <c r="D920">
+        <v>4933.64</v>
+      </c>
+      <c r="E920">
+        <v>3588.88</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_metalls.xlsx
+++ b/LME/parser/cbr/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E920"/>
+  <dimension ref="A1:E921"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -16033,6 +16033,23 @@
         <v>3588.88</v>
       </c>
     </row>
+    <row r="921" spans="1:5">
+      <c r="A921" s="2">
+        <v>46289</v>
+      </c>
+      <c r="B921">
+        <v>11747.89</v>
+      </c>
+      <c r="C921">
+        <v>178.1</v>
+      </c>
+      <c r="D921">
+        <v>4922.42</v>
+      </c>
+      <c r="E921">
+        <v>3575.34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_metalls.xlsx
+++ b/LME/parser/cbr/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E921"/>
+  <dimension ref="A1:E922"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -16050,6 +16050,23 @@
         <v>3575.34</v>
       </c>
     </row>
+    <row r="922" spans="1:5">
+      <c r="A922" s="2">
+        <v>46290</v>
+      </c>
+      <c r="B922">
+        <v>11695.6</v>
+      </c>
+      <c r="C922">
+        <v>177.94</v>
+      </c>
+      <c r="D922">
+        <v>4826.52</v>
+      </c>
+      <c r="E922">
+        <v>3472.96</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_metalls.xlsx
+++ b/LME/parser/cbr/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E922"/>
+  <dimension ref="A1:E923"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -16067,6 +16067,23 @@
         <v>3472.96</v>
       </c>
     </row>
+    <row r="923" spans="1:5">
+      <c r="A923" s="2">
+        <v>46291</v>
+      </c>
+      <c r="B923">
+        <v>11568.93</v>
+      </c>
+      <c r="C923">
+        <v>172.41</v>
+      </c>
+      <c r="D923">
+        <v>4755.13</v>
+      </c>
+      <c r="E923">
+        <v>3443.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_metalls.xlsx
+++ b/LME/parser/cbr/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E923"/>
+  <dimension ref="A1:E924"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -16084,6 +16084,23 @@
         <v>3443.1</v>
       </c>
     </row>
+    <row r="924" spans="1:5">
+      <c r="A924" s="2">
+        <v>46294</v>
+      </c>
+      <c r="B924">
+        <v>11563.48</v>
+      </c>
+      <c r="C924">
+        <v>176.44</v>
+      </c>
+      <c r="D924">
+        <v>4800.1</v>
+      </c>
+      <c r="E924">
+        <v>3410.52</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_metalls.xlsx
+++ b/LME/parser/cbr/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E924"/>
+  <dimension ref="A1:E925"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -16101,6 +16101,23 @@
         <v>3410.52</v>
       </c>
     </row>
+    <row r="925" spans="1:5">
+      <c r="A925" s="2">
+        <v>46295</v>
+      </c>
+      <c r="B925">
+        <v>11250.09</v>
+      </c>
+      <c r="C925">
+        <v>166.48</v>
+      </c>
+      <c r="D925">
+        <v>4700.99</v>
+      </c>
+      <c r="E925">
+        <v>3309.57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_metalls.xlsx
+++ b/LME/parser/cbr/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E925"/>
+  <dimension ref="A1:E926"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -16118,6 +16118,23 @@
         <v>3309.57</v>
       </c>
     </row>
+    <row r="926" spans="1:5">
+      <c r="A926" s="2">
+        <v>46296</v>
+      </c>
+      <c r="B926">
+        <v>11184.87</v>
+      </c>
+      <c r="C926">
+        <v>163.51</v>
+      </c>
+      <c r="D926">
+        <v>4540.82</v>
+      </c>
+      <c r="E926">
+        <v>3273.74</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_metalls.xlsx
+++ b/LME/parser/cbr/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E926"/>
+  <dimension ref="A1:E927"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -16135,6 +16135,23 @@
         <v>3273.74</v>
       </c>
     </row>
+    <row r="927" spans="1:5">
+      <c r="A927" s="2">
+        <v>46297</v>
+      </c>
+      <c r="B927">
+        <v>11177.45</v>
+      </c>
+      <c r="C927">
+        <v>162.54</v>
+      </c>
+      <c r="D927">
+        <v>4587.62</v>
+      </c>
+      <c r="E927">
+        <v>3270.56</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_metalls.xlsx
+++ b/LME/parser/cbr/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E927"/>
+  <dimension ref="A1:E928"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -16152,6 +16152,23 @@
         <v>3270.56</v>
       </c>
     </row>
+    <row r="928" spans="1:5">
+      <c r="A928" s="2">
+        <v>46298</v>
+      </c>
+      <c r="B928">
+        <v>11143.31</v>
+      </c>
+      <c r="C928">
+        <v>163.51</v>
+      </c>
+      <c r="D928">
+        <v>4636.32</v>
+      </c>
+      <c r="E928">
+        <v>3204.64</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_metalls.xlsx
+++ b/LME/parser/cbr/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E928"/>
+  <dimension ref="A1:E929"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -16169,6 +16169,23 @@
         <v>3204.64</v>
       </c>
     </row>
+    <row r="929" spans="1:5">
+      <c r="A929" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B929">
+        <v>11441.31</v>
+      </c>
+      <c r="C929">
+        <v>166.66</v>
+      </c>
+      <c r="D929">
+        <v>4761.6</v>
+      </c>
+      <c r="E929">
+        <v>3267.29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_metalls.xlsx
+++ b/LME/parser/cbr/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E929"/>
+  <dimension ref="A1:E930"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -16186,6 +16186,23 @@
         <v>3267.29</v>
       </c>
     </row>
+    <row r="930" spans="1:5">
+      <c r="A930" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B930">
+        <v>11413.1</v>
+      </c>
+      <c r="C930">
+        <v>170.34</v>
+      </c>
+      <c r="D930">
+        <v>4771.89</v>
+      </c>
+      <c r="E930">
+        <v>3255.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_metalls.xlsx
+++ b/LME/parser/cbr/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E930"/>
+  <dimension ref="A1:E931"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -16203,6 +16203,23 @@
         <v>3255.99</v>
       </c>
     </row>
+    <row r="931" spans="1:5">
+      <c r="A931" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B931">
+        <v>11422.95</v>
+      </c>
+      <c r="C931">
+        <v>167.65</v>
+      </c>
+      <c r="D931">
+        <v>4675.78</v>
+      </c>
+      <c r="E931">
+        <v>3199.82</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_metalls.xlsx
+++ b/LME/parser/cbr/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E931"/>
+  <dimension ref="A1:E932"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -16220,6 +16220,23 @@
         <v>3199.82</v>
       </c>
     </row>
+    <row r="932" spans="1:5">
+      <c r="A932" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B932">
+        <v>11246.9</v>
+      </c>
+      <c r="C932">
+        <v>165.01</v>
+      </c>
+      <c r="D932">
+        <v>4455.21</v>
+      </c>
+      <c r="E932">
+        <v>3086.35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_metalls.xlsx
+++ b/LME/parser/cbr/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E932"/>
+  <dimension ref="A1:E933"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -16237,6 +16237,23 @@
         <v>3086.35</v>
       </c>
     </row>
+    <row r="933" spans="1:5">
+      <c r="A933" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B933">
+        <v>11258.99</v>
+      </c>
+      <c r="C933">
+        <v>160.65</v>
+      </c>
+      <c r="D933">
+        <v>4487.3</v>
+      </c>
+      <c r="E933">
+        <v>3070.29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_metalls.xlsx
+++ b/LME/parser/cbr/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E933"/>
+  <dimension ref="A1:E934"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -16254,6 +16254,23 @@
         <v>3070.29</v>
       </c>
     </row>
+    <row r="934" spans="1:5">
+      <c r="A934" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B934">
+        <v>11294.38</v>
+      </c>
+      <c r="C934">
+        <v>162.42</v>
+      </c>
+      <c r="D934">
+        <v>4518.37</v>
+      </c>
+      <c r="E934">
+        <v>3078.89</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_metalls.xlsx
+++ b/LME/parser/cbr/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E934"/>
+  <dimension ref="A1:E935"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -16271,6 +16271,23 @@
         <v>3078.89</v>
       </c>
     </row>
+    <row r="935" spans="1:5">
+      <c r="A935" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B935">
+        <v>11249.11</v>
+      </c>
+      <c r="C935">
+        <v>163.47</v>
+      </c>
+      <c r="D935">
+        <v>4554.09</v>
+      </c>
+      <c r="E935">
+        <v>3103.02</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_metalls.xlsx
+++ b/LME/parser/cbr/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E935"/>
+  <dimension ref="A1:E936"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -16288,6 +16288,23 @@
         <v>3103.02</v>
       </c>
     </row>
+    <row r="936" spans="1:5">
+      <c r="A936" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B936">
+        <v>11253.66</v>
+      </c>
+      <c r="C936">
+        <v>162.51</v>
+      </c>
+      <c r="D936">
+        <v>4559.36</v>
+      </c>
+      <c r="E936">
+        <v>3050.05</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_metalls.xlsx
+++ b/LME/parser/cbr/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E936"/>
+  <dimension ref="A1:E937"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -16305,6 +16305,23 @@
         <v>3050.05</v>
       </c>
     </row>
+    <row r="937" spans="1:5">
+      <c r="A937" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B937">
+        <v>11012.12</v>
+      </c>
+      <c r="C937">
+        <v>157.51</v>
+      </c>
+      <c r="D937">
+        <v>4403.77</v>
+      </c>
+      <c r="E937">
+        <v>3009.63</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_metalls.xlsx
+++ b/LME/parser/cbr/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E937"/>
+  <dimension ref="A1:E938"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -16322,6 +16322,23 @@
         <v>3009.63</v>
       </c>
     </row>
+    <row r="938" spans="1:5">
+      <c r="A938" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B938">
+        <v>11162.78</v>
+      </c>
+      <c r="C938">
+        <v>152.47</v>
+      </c>
+      <c r="D938">
+        <v>4353.95</v>
+      </c>
+      <c r="E938">
+        <v>3036.51</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_metalls.xlsx
+++ b/LME/parser/cbr/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E938"/>
+  <dimension ref="A1:E939"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -16339,6 +16339,23 @@
         <v>3036.51</v>
       </c>
     </row>
+    <row r="939" spans="1:5">
+      <c r="A939" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B939">
+        <v>11158.77</v>
+      </c>
+      <c r="C939">
+        <v>153.71</v>
+      </c>
+      <c r="D939">
+        <v>4368.2</v>
+      </c>
+      <c r="E939">
+        <v>3006.12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_metalls.xlsx
+++ b/LME/parser/cbr/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E939"/>
+  <dimension ref="A1:E940"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -16356,6 +16356,23 @@
         <v>3006.12</v>
       </c>
     </row>
+    <row r="940" spans="1:5">
+      <c r="A940" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B940">
+        <v>11053.5</v>
+      </c>
+      <c r="C940">
+        <v>153.61</v>
+      </c>
+      <c r="D940">
+        <v>4382.97</v>
+      </c>
+      <c r="E940">
+        <v>3016.27</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_metalls.xlsx
+++ b/LME/parser/cbr/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E940"/>
+  <dimension ref="A1:E941"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -16373,6 +16373,23 @@
         <v>3016.27</v>
       </c>
     </row>
+    <row r="941" spans="1:5">
+      <c r="A941" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B941">
+        <v>10870.2</v>
+      </c>
+      <c r="C941">
+        <v>150.49</v>
+      </c>
+      <c r="D941">
+        <v>4308.55</v>
+      </c>
+      <c r="E941">
+        <v>2910.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_metalls.xlsx
+++ b/LME/parser/cbr/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E941"/>
+  <dimension ref="A1:E942"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -16390,6 +16390,23 @@
         <v>2910.4</v>
       </c>
     </row>
+    <row r="942" spans="1:5">
+      <c r="A942" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B942">
+        <v>10765.26</v>
+      </c>
+      <c r="C942">
+        <v>150.09</v>
+      </c>
+      <c r="D942">
+        <v>4267.61</v>
+      </c>
+      <c r="E942">
+        <v>2850.03</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_metalls.xlsx
+++ b/LME/parser/cbr/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E942"/>
+  <dimension ref="A1:E943"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -16407,6 +16407,23 @@
         <v>2850.03</v>
       </c>
     </row>
+    <row r="943" spans="1:5">
+      <c r="A943" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B943">
+        <v>10482.37</v>
+      </c>
+      <c r="C943">
+        <v>144.58</v>
+      </c>
+      <c r="D943">
+        <v>4104.39</v>
+      </c>
+      <c r="E943">
+        <v>2755.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_metalls.xlsx
+++ b/LME/parser/cbr/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E943"/>
+  <dimension ref="A1:E944"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -16424,6 +16424,23 @@
         <v>2755.21</v>
       </c>
     </row>
+    <row r="944" spans="1:5">
+      <c r="A944" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B944">
+        <v>10385.78</v>
+      </c>
+      <c r="C944">
+        <v>139.48</v>
+      </c>
+      <c r="D944">
+        <v>4033.41</v>
+      </c>
+      <c r="E944">
+        <v>2730.04</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_metalls.xlsx
+++ b/LME/parser/cbr/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E944"/>
+  <dimension ref="A1:E945"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -16441,6 +16441,23 @@
         <v>2730.04</v>
       </c>
     </row>
+    <row r="945" spans="1:5">
+      <c r="A945" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B945">
+        <v>10417.84</v>
+      </c>
+      <c r="C945">
+        <v>139.94</v>
+      </c>
+      <c r="D945">
+        <v>3936.37</v>
+      </c>
+      <c r="E945">
+        <v>2722.33</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_metalls.xlsx
+++ b/LME/parser/cbr/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E945"/>
+  <dimension ref="A1:E946"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -16458,6 +16458,23 @@
         <v>2722.33</v>
       </c>
     </row>
+    <row r="946" spans="1:5">
+      <c r="A946" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B946">
+        <v>10548.5</v>
+      </c>
+      <c r="C946">
+        <v>138.5</v>
+      </c>
+      <c r="D946">
+        <v>3960.32</v>
+      </c>
+      <c r="E946">
+        <v>2666.86</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_metalls.xlsx
+++ b/LME/parser/cbr/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E946"/>
+  <dimension ref="A1:E947"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -16475,6 +16475,23 @@
         <v>2666.86</v>
       </c>
     </row>
+    <row r="947" spans="1:5">
+      <c r="A947" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B947">
+        <v>10484.12</v>
+      </c>
+      <c r="C947">
+        <v>139.47</v>
+      </c>
+      <c r="D947">
+        <v>4014.03</v>
+      </c>
+      <c r="E947">
+        <v>2640.48</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_metalls.xlsx
+++ b/LME/parser/cbr/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E947"/>
+  <dimension ref="A1:E948"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -16492,6 +16492,23 @@
         <v>2640.48</v>
       </c>
     </row>
+    <row r="948" spans="1:5">
+      <c r="A948" s="2">
+        <v>46326</v>
+      </c>
+      <c r="B948">
+        <v>10428.02</v>
+      </c>
+      <c r="C948">
+        <v>135.77</v>
+      </c>
+      <c r="D948">
+        <v>3841.84</v>
+      </c>
+      <c r="E948">
+        <v>2602.67</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
